--- a/infor-beta/templates/INFOR Comps Template.xlsx
+++ b/infor-beta/templates/INFOR Comps Template.xlsx
@@ -1263,6 +1263,13 @@
     <definedName name="Z_87743AA5_80A6_11D3_8889_0000832DEAF9_.wvu.Cols" hidden="1">#REF!,#REF!</definedName>
     <definedName name="Z_87743AA5_80A6_11D3_8889_0000832DEAF9_.wvu.PrintTitles" hidden="1">#REF!,#REF!</definedName>
     <definedName name="Z_87743AA5_80A6_11D3_8889_0000832DEAF9_.wvu.Rows" hidden="1">#REF!,#REF!,#REF!,#REF!,#REF!,#REF!,#REF!</definedName>
+    <definedName name="infor_comps_group1_block" localSheetId="1">'Comps'!$B$10:$AA$15</definedName>
+    <definedName name="infor_comps_group1_label" localSheetId="1">'Comps'!$D$9</definedName>
+    <definedName name="infor_comps_group2_block" localSheetId="1">'Comps'!$B$20:$AA$25</definedName>
+    <definedName name="infor_comps_group2_label" localSheetId="1">'Comps'!$D$19</definedName>
+    <definedName name="infor_comps_group3_block" localSheetId="1">'Comps'!$B$30:$AA$35</definedName>
+    <definedName name="infor_comps_group3_label" localSheetId="1">'Comps'!$D$29</definedName>
+    <definedName name="infor_comps_output_ccy" localSheetId="1">'Comps'!$F$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
